--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IXC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IXC" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -461,6 +461,31 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1082</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,31 @@
         <v>1082</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1048</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,31 @@
         <v>1048</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,31 @@
         <v>1335</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,31 @@
         <v>1114</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -586,6 +586,31 @@
         <v>934</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,6 +611,56 @@
         <v>1108</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1262</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,6 +661,31 @@
         <v>1262</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1072</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -686,6 +686,31 @@
         <v>1072</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/IXComercio.xlsx
+++ b/IXComercio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -711,6 +711,31 @@
         <v>1108</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Total ordenes IX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
